--- a/data/trans_orig/IP07_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_R2-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1757</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3351</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7744</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7457</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3993</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9076</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148265</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>143916</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>150501</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135375</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130982</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137402</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131269</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137417</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148265</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>143182</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278215</t>
+          <t>277840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287175</t>
+          <t>287098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>152258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>152258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>152258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>152258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>152258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>152258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12140</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18167</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4432</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9518</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12140</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7402</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18183</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>198655</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>192628</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>203297</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>190731</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>185645</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193249</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>186215</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>193280</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>198655</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>192612</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>203393</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381235</t>
+          <t>381970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394642</t>
+          <t>395138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210795</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210795</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210795</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210795</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210795</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7348</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2387</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7760</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146345</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142309</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>135430</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131913</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>137364</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>132352</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>137195</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>146345</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141897</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148368</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276771</t>
+          <t>277294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284887</t>
+          <t>284852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2647</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10424</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1474</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5313</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11254</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13189</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201211</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196756</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204533</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207841</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>204194</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>204002</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201211</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>195926</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>204445</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>568</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>403306</t>
+          <t>403726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412511</t>
+          <t>412548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207180</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207180</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207180</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207180</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207180</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,74 +2095,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18490</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35297</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7265</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18649</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18628</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18030</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>33821</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>28607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>694476</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>684593</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>701400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>669376</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>662372</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>673756</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>662393</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>674153</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>694476</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>686069</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>701860</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1353957</t>
+          <t>1353306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1373378</t>
+          <t>1372304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5375</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4102</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8704</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5360</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>151872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148470</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153226</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>134519</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>129917</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137666</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>129834</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137252</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>151872</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148485</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153212</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280857</t>
+          <t>280958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289555</t>
+          <t>289880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138621</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138621</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138621</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2666</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6773</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6372</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7221</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>219124</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>215134</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221092</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203692</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199585</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>205147</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>199986</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>205680</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>219124</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>215175</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221093</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416866</t>
+          <t>418654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425539</t>
+          <t>426081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>222396</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>222396</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>222396</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>222396</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>222396</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>222396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6320</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11298</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4773</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2183</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8927</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9269</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6320</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11693</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>160272</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155294</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163491</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>149905</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>145751</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152495</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>145409</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152468</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>160272</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154899</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>163309</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304400</t>
+          <t>304322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314662</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154678</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154678</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154678</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13294</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5079</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10061</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9711</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3551</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12585</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199853</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>193719</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>203351</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204434</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>199452</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207392</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>199802</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>207318</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199853</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>194428</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>203462</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397854</t>
+          <t>396221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409374</t>
+          <t>408799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207013</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207013</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207013</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207013</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207013</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207013</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12486</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26716</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10563</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24280</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10857</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24748</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13095</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26308</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46783</t>
+          <t>46163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>731120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>723130</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>737360</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>998</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>692551</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>698607</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>684422</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>698313</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>731120</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>723538</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>736751</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1412233</t>
+          <t>1412853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1432818</t>
+          <t>1431978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3844</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8823</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9174</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144165</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>139291</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>146220</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>129181</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124202</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131755</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>123851</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131744</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144165</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>139807</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>146646</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>371</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267495</t>
+          <t>267944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>276960</t>
+          <t>277195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147308</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147308</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147308</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133025</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133025</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133025</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147308</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147308</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8632</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4277</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8884</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1772</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8768</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>218804</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>214321</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221465</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>201820</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>197213</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>204249</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>197576</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>204325</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>218804</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>214185</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221373</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414672</t>
+          <t>414851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>424476</t>
+          <t>424399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>222953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>222953</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>222953</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206097</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206097</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206097</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>222953</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>222953</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>222953</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5391</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2527</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10175</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6582</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7267</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5391</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10637</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161282</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156498</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164146</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151511</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148049</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153506</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>147364</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153495</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161282</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>156036</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164096</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>492</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306824</t>
+          <t>307382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316425</t>
+          <t>316608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154631</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154631</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154631</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2816</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2157</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6110</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5979</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2816</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7084</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202274</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198049</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204379</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>203862</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>199909</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>200040</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205437</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,72%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202274</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>198006</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>204278</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>561</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401339</t>
+          <t>401350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409021</t>
+          <t>408993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205090</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205090</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205090</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206019</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206019</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206019</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205090</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205090</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23187</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8737</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21336</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8496</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20805</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9417</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>22821</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>37817</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>726525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>718837</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>732440</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>686375</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>678437</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>691036</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>691277</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>726525</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>719203</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>732607</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1403464</t>
+          <t>1403980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1420876</t>
+          <t>1420256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10767</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3134</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8176</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122087</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>115139</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124606</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>114146</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>109104</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116312</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>136426</t>
+          <t>117900</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129715</t>
+          <t>113148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139027</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>250573</t>
+          <t>239987</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243413</t>
+          <t>233452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254201</t>
+          <t>243685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4708</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8834</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11210</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4117</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31923</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40814</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>232498</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>228372</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>235137</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>179302</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>158589</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>186395</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>249638</t>
+          <t>178362</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>244674</t>
+          <t>173129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252798</t>
+          <t>182005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>428940</t>
+          <t>410860</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404734</t>
+          <t>404667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>436933</t>
+          <t>415654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1544</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9086</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165828</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160936</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167680</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>186018</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>181315</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>188857</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>182553</t>
+          <t>152499</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177520</t>
+          <t>147398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184530</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>368572</t>
+          <t>318327</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>362316</t>
+          <t>311936</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372585</t>
+          <t>322283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2979</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11332</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2417</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163285</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158044</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166397</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>165545</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161889</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167196</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>174685</t>
+          <t>164777</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169449</t>
+          <t>160656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178621</t>
+          <t>166450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>328062</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333281</t>
+          <t>321959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344690</t>
+          <t>332102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25332</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12880</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44185</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>683698</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>675497</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>690065</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>645011</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>621970</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>653275</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>743303</t>
+          <t>613538</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734417</t>
+          <t>605552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>750007</t>
+          <t>619734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1388314</t>
+          <t>1297237</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1365880</t>
+          <t>1286599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400058</t>
+          <t>1305830</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
